--- a/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
@@ -608,7 +608,7 @@
               <rFont val="Arial"/>
               <family val="2"/>
             </rPr>
-            <t xml:space="preserve"> trust'.</t>
+            <t xml:space="preserve"> trust.</t>
           </r>
         </is>
       </c>
@@ -652,7 +652,7 @@
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONCERT</t>
+          <t xml:space="preserve">CONCERT®</t>
         </is>
       </c>
     </row>

--- a/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
@@ -17,6 +17,19 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="25.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -37,19 +50,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -121,39 +121,39 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -288,14 +288,14 @@
   <sheetData>
     <row r="1" ht="37.77" customHeight="1"/>
     <row r="2" ht="30.60" customHeight="1">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MYRIAD</t>
         </is>
       </c>
     </row>
     <row r="3" ht="11.40" customHeight="1">
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
@@ -303,7 +303,7 @@
     </row>
     <row r="4" ht="62.75" customHeight="1"/>
     <row r="5" ht="17.40" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Myriad - Prices at a Glance</t>
         </is>
@@ -311,7 +311,7 @@
     </row>
     <row r="6" ht="7.54" customHeight="1"/>
     <row r="7" ht="12.60" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">October 2021</t>
         </is>
@@ -319,200 +319,200 @@
     </row>
     <row r="8" ht="35.42" customHeight="1"/>
     <row r="9" ht="23.96" customHeight="1">
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Suite Type</t>
         </is>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Plan</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Square Feet</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Starting From</t>
         </is>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" ht="25.50" customHeight="1">
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom</t>
         </is>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AT*</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">476 - 479</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$449,900</t>
         </is>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">B1 - B7</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">518 - 689</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$499,900</t>
         </is>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" ht="22.26" customHeight="1">
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Bedroom + Den</t>
         </is>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">C1 - C6</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">644 - 769</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$599,900</t>
         </is>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" ht="23.51" customHeight="1">
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom</t>
         </is>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">D1 - D7</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801-989</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801 - 989</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$729,900</t>
         </is>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" ht="24.53" customHeight="1">
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Two Bedroom + Den</t>
         </is>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">E1 - E7</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">834 - 1,062</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$749,900</t>
         </is>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" ht="23.76" customHeight="1">
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Three Bedroom</t>
         </is>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,023</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$929,900</t>
         </is>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" ht="22.27" customHeight="1">
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Townhomes</t>
         </is>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TH1 - TH4</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,338 - 1,553</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$1,249,900</t>
         </is>
       </c>
-      <c r="I16" s="6"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" ht="37.68" customHeight="1"/>
     <row r="18" ht="11.40" customHeight="1">
@@ -658,10 +658,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="C10:E10"/>
@@ -678,6 +674,10 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
     <mergeCell ref="C18:J18"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E21:J21"/>

--- a/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
@@ -30,7 +30,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="25.5"/>
+      <sz val="22.7"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -276,14 +276,11 @@
   <cols>
     <col min="1" max="1" width="6.95" customWidth="1"/>
     <col min="2" max="2" width="0.30" customWidth="1"/>
-    <col min="3" max="3" width="0.81" customWidth="1"/>
-    <col min="4" max="4" width="0.30" customWidth="1"/>
-    <col min="5" max="5" width="21.81" customWidth="1"/>
-    <col min="6" max="6" width="15.28" customWidth="1"/>
-    <col min="7" max="7" width="19.06" customWidth="1"/>
-    <col min="8" max="8" width="6.92" customWidth="1"/>
-    <col min="9" max="9" width="10.72" customWidth="1"/>
-    <col min="10" max="10" width="2.21" customWidth="1"/>
+    <col min="3" max="3" width="24.14" customWidth="1"/>
+    <col min="4" max="4" width="15.28" customWidth="1"/>
+    <col min="5" max="5" width="19.06" customWidth="1"/>
+    <col min="6" max="6" width="18.36" customWidth="1"/>
+    <col min="7" max="7" width="2.21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="37.77" customHeight="1"/>
@@ -295,7 +292,7 @@
       </c>
     </row>
     <row r="3" ht="11.40" customHeight="1">
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">HEART OF BURQUITLAM</t>
         </is>
@@ -324,24 +321,21 @@
           <t xml:space="preserve">Suite Type</t>
         </is>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Square Feet</t>
+        </is>
+      </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square Feet</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Starting From</t>
         </is>
       </c>
-      <c r="I9" s="1"/>
     </row>
     <row r="10" ht="25.50" customHeight="1">
       <c r="C10" s="2" t="inlineStr">
@@ -349,45 +343,39 @@
           <t xml:space="preserve">One Bedroom</t>
         </is>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT*</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">476 - 479</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AT*</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">476 - 479</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$449,900</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
     </row>
     <row r="11" ht="21.85" customHeight="1">
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B1 - B7</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518 - 689</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1 - B7</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518 - 689</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$499,900</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
     </row>
     <row r="12" ht="22.26" customHeight="1">
       <c r="C12" s="2" t="inlineStr">
@@ -395,24 +383,21 @@
           <t xml:space="preserve">One Bedroom + Den</t>
         </is>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C1 - C6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">644 - 769</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1 - C6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">644 - 769</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$599,900</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
     </row>
     <row r="13" ht="23.51" customHeight="1">
       <c r="C13" s="2" t="inlineStr">
@@ -420,24 +405,21 @@
           <t xml:space="preserve">Two Bedroom</t>
         </is>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1 - D7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801 - 989</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1 - D7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801 - 989</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$729,900</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
     </row>
     <row r="14" ht="24.53" customHeight="1">
       <c r="C14" s="2" t="inlineStr">
@@ -445,24 +427,21 @@
           <t xml:space="preserve">Two Bedroom + Den</t>
         </is>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1 - E7</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834 - 1,062</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1 - E7</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834 - 1,062</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$749,900</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
     </row>
     <row r="15" ht="23.76" customHeight="1">
       <c r="C15" s="2" t="inlineStr">
@@ -470,24 +449,21 @@
           <t xml:space="preserve">Three Bedroom</t>
         </is>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,023</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1,023</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$929,900</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
     </row>
     <row r="16" ht="22.27" customHeight="1">
       <c r="C16" s="2" t="inlineStr">
@@ -495,24 +471,21 @@
           <t xml:space="preserve">Townhomes</t>
         </is>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TH1 - TH4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,338 - 1,553</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TH1 - TH4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1,338 - 1,553</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">$1,249,900</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
     </row>
     <row r="17" ht="37.68" customHeight="1"/>
     <row r="18" ht="11.40" customHeight="1">
@@ -524,14 +497,14 @@
     </row>
     <row r="19" ht="11.60" customHeight="1"/>
     <row r="20" ht="12.60" customHeight="1">
-      <c r="E20" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  Initial $10,000 bank draft due upon signing Offer to Purchase and Agreement Sale;</t>
         </is>
       </c>
     </row>
     <row r="21" ht="11.82" customHeight="1">
-      <c r="E21" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% within 7 days (less $10,000 initial deposit) upon signing;</t>
         </is>
@@ -539,21 +512,21 @@
     </row>
     <row r="22" ht="2.61" customHeight="1"/>
     <row r="23" ht="12.00" customHeight="1">
-      <c r="E23" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 180 days;</t>
         </is>
       </c>
     </row>
     <row r="24" ht="13.20" customHeight="1">
-      <c r="E24" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 365 days;</t>
         </is>
       </c>
     </row>
     <row r="25" ht="13.05" customHeight="1">
-      <c r="E25" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% in 730 days.</t>
         </is>
@@ -561,7 +534,7 @@
     </row>
     <row r="26" ht="2.22" customHeight="1"/>
     <row r="27" ht="12.60" customHeight="1">
-      <c r="E27" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -650,47 +623,31 @@
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="E25:J25"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:J35"/>
+  <mergeCells count="17">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="F35:G35"/>
   </mergeCells>
   <pageMargins left="0.55" right="1.08" top="0.48" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
+++ b/ios/Verification/office-layout/OfficeSamplePriceList.xlsx
@@ -115,10 +115,10 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -496,14 +496,14 @@
       </c>
     </row>
     <row r="19" ht="11.60" customHeight="1"/>
-    <row r="20" ht="12.60" customHeight="1">
+    <row r="20" ht="11.82" customHeight="1">
       <c r="C20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  Initial $10,000 bank draft due upon signing Offer to Purchase and Agreement Sale;</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="11.82" customHeight="1">
+    <row r="21" ht="12.60" customHeight="1">
       <c r="C21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">•  5% within 7 days (less $10,000 initial deposit) upon signing;</t>
@@ -532,9 +532,8 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="2.22" customHeight="1"/>
-    <row r="27" ht="12.60" customHeight="1">
-      <c r="C27" s="8" t="inlineStr">
+    <row r="26" ht="14.82" customHeight="1">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -586,44 +585,43 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="58.49" customHeight="1"/>
+    <row r="27" ht="58.49" customHeight="1"/>
+    <row r="28" ht="7.06" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prices do not include CST, may change without notice and are subject to availability Suite sizes may vary on final Strata Plan. Concert reserves the right to</t>
+        </is>
+      </c>
+    </row>
     <row r="29" ht="7.67" customHeight="1">
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prices do not include CST, may change without notice and are subject to availability Suite sizes may vary on final Strata Plan. Concert reserves the right to</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="7.06" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
-        <is>
           <t xml:space="preserve">make modifications and changes to floorplans, project design, specifications and features. October 2021 CONCERT REALTY SERVICES LTD E.80 E</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="57.46" customHeight="1"/>
+    <row r="30" ht="57.46" customHeight="1"/>
+    <row r="31" ht="9.47" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MyriadbyConcert.com</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="10.03" customHeight="1">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MyriadbyConcert.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="9.47" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">101 - 511 Clarke Road, Coquitlam, BC V3J 0J1</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="2.02" customHeight="1"/>
-    <row r="35" ht="9.60" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
+    <row r="33" ht="11.62" customHeight="1">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">604.335.0696 | Admin.Myriad@ConcertProperties.com</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">CONCERT®</t>
         </is>
@@ -641,13 +639,13 @@
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <pageMargins left="0.55" right="1.08" top="0.48" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
